--- a/player_schedules.xlsx
+++ b/player_schedules.xlsx
@@ -935,7 +935,7 @@
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>LAX01</t>
+          <t>MEL00</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
@@ -7009,7 +7009,7 @@
       <c r="AR46" t="inlineStr"/>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>DAL00</t>
+          <t>RIO00</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr">
@@ -7096,10 +7096,10 @@
         <v>7</v>
       </c>
       <c r="Y47" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="Z47" t="n">
-        <v>-180</v>
+        <v>-185</v>
       </c>
       <c r="AA47" t="n">
         <v>3.5</v>
@@ -7719,7 +7719,7 @@
       <c r="AR51" t="inlineStr"/>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>WAS00</t>
+          <t>LON02</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr">
@@ -10212,10 +10212,10 @@
         <v>7</v>
       </c>
       <c r="Y69" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="Z69" t="n">
-        <v>-410</v>
+        <v>-395</v>
       </c>
       <c r="AA69" t="n">
         <v>8.5</v>
@@ -12105,7 +12105,7 @@
       <c r="AR82" t="inlineStr"/>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>JAX00</t>
+          <t>LON00</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr">
@@ -14085,7 +14085,7 @@
       <c r="AR96" t="inlineStr"/>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>NOR00</t>
+          <t>PAR00</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr">
@@ -17689,7 +17689,7 @@
       <c r="AR124" t="inlineStr"/>
       <c r="AS124" t="inlineStr">
         <is>
-          <t>ATL97</t>
+          <t>MAD01</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr">
@@ -19591,7 +19591,7 @@
       <c r="AR139" t="inlineStr"/>
       <c r="AS139" t="inlineStr">
         <is>
-          <t>DET00</t>
+          <t>MUN01</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr">
@@ -22607,7 +22607,7 @@
       <c r="AR163" t="inlineStr"/>
       <c r="AS163" t="inlineStr">
         <is>
-          <t>SFO01</t>
+          <t>MEX00</t>
         </is>
       </c>
       <c r="AT163" t="inlineStr">
